--- a/artfynd/A 35801-2020 artfynd.xlsx
+++ b/artfynd/A 35801-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839320</v>
+        <v>119839322</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541478</v>
+        <v>541521</v>
       </c>
       <c r="R3" t="n">
-        <v>6969365</v>
+        <v>6969412</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839322</v>
+        <v>119839320</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541521</v>
+        <v>541478</v>
       </c>
       <c r="R4" t="n">
-        <v>6969412</v>
+        <v>6969365</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 35801-2020 artfynd.xlsx
+++ b/artfynd/A 35801-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839322</v>
+        <v>119839320</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541521</v>
+        <v>541478</v>
       </c>
       <c r="R3" t="n">
-        <v>6969412</v>
+        <v>6969365</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839320</v>
+        <v>119839322</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541478</v>
+        <v>541521</v>
       </c>
       <c r="R4" t="n">
-        <v>6969365</v>
+        <v>6969412</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 35801-2020 artfynd.xlsx
+++ b/artfynd/A 35801-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839321</v>
+        <v>119839320</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541507</v>
+        <v>541478</v>
       </c>
       <c r="R2" t="n">
-        <v>6969402</v>
+        <v>6969365</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839320</v>
+        <v>119839321</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>89269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541478</v>
+        <v>541507</v>
       </c>
       <c r="R3" t="n">
-        <v>6969365</v>
+        <v>6969402</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,7 +882,7 @@
         <v>119839322</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 35801-2020 artfynd.xlsx
+++ b/artfynd/A 35801-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839320</v>
+        <v>119839322</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541478</v>
+        <v>541521</v>
       </c>
       <c r="R2" t="n">
-        <v>6969365</v>
+        <v>6969412</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839322</v>
+        <v>119839320</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541521</v>
+        <v>541478</v>
       </c>
       <c r="R4" t="n">
-        <v>6969412</v>
+        <v>6969365</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 35801-2020 artfynd.xlsx
+++ b/artfynd/A 35801-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839322</v>
+        <v>119839321</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541521</v>
+        <v>541507</v>
       </c>
       <c r="R2" t="n">
-        <v>6969412</v>
+        <v>6969402</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839321</v>
+        <v>119839322</v>
       </c>
       <c r="B3" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541507</v>
+        <v>541521</v>
       </c>
       <c r="R3" t="n">
-        <v>6969402</v>
+        <v>6969412</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
